--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:23</t>
+    <t xml:space="preserve">2026-09-10 01:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:37</t>
+    <t xml:space="preserve">2026-09-18 11:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:33</t>
+    <t xml:space="preserve">2026-09-23 15:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Fernandez</t>
+    <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
     <t xml:space="preserve">Puchuncaví</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:38</t>
+    <t xml:space="preserve">2026-10-04 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:48</t>
+    <t xml:space="preserve">2026-10-05 16:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1237,7 +1237,7 @@
         <v>62.62</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>100.08</v>
+        <v>100.09</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>106.96</v>
